--- a/data/trans_dic/P25C$otraforma_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 7,43</t>
+          <t>0,59; 7,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,81</t>
+          <t>0,52; 5,09</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,0</t>
+          <t>0,93; 9,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,77</t>
+          <t>0,65; 5,89</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,4</t>
+          <t>0,0; 14,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,49</t>
+          <t>2,08; 8,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 9,5</t>
+          <t>0,81; 8,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,18</t>
+          <t>2,13; 7,1</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 14,83</t>
+          <t>2,83; 15,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 13,02</t>
+          <t>2,64; 12,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,49</t>
+          <t>3,66; 11,25</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,43</t>
+          <t>0,0; 74,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,89</t>
+          <t>0,0; 9,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,38</t>
+          <t>0,0; 14,04</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,85</t>
+          <t>1,08; 4,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,65</t>
+          <t>1,56; 4,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,14</t>
+          <t>1,37; 4,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>711; 9168</t>
+          <t>728; 8913</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4083</t>
+          <t>0; 3467</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>721; 9061</t>
+          <t>979; 9589</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>946; 8393</t>
+          <t>870; 8484</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1221</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>948; 8659</t>
+          <t>973; 8829</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 11365</t>
+          <t>0; 11425</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2921</t>
+          <t>0; 3266</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 12387</t>
+          <t>0; 12017</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3727; 16075</t>
+          <t>3938; 15834</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>643; 7507</t>
+          <t>639; 6754</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5794; 19261</t>
+          <t>5716; 19055</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2878; 13060</t>
+          <t>2488; 13519</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1957; 9126</t>
+          <t>1848; 8572</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5951; 18175</t>
+          <t>5789; 17792</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5054</t>
+          <t>0; 5181</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3685</t>
+          <t>0; 3568</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5477</t>
+          <t>0; 6211</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9844; 40750</t>
+          <t>9082; 39461</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5241; 15338</t>
+          <t>5131; 14945</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15773; 48418</t>
+          <t>16077; 50284</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otraforma_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,22</t>
+          <t>0,65; 6,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,09</t>
+          <t>0,54; 5,04</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,09</t>
+          <t>1,11; 10,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,89</t>
+          <t>0,72; 6,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,92; 7,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 18,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,79; 6,9</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,37</t>
+          <t>1,86; 8,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,55</t>
+          <t>0,82; 9,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 7,1</t>
+          <t>2,45; 6,98</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 15,35</t>
+          <t>2,54; 13,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 12,23</t>
+          <t>2,51; 11,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 11,25</t>
+          <t>3,67; 10,8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,25</t>
+          <t>0,0; 62,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,58</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,04</t>
+          <t>0,0; 12,47</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,69</t>
+          <t>2,88; 6,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,53</t>
+          <t>1,45; 4,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,3</t>
+          <t>2,77; 5,1</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>705</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3874</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>728; 8913</t>
+          <t>852; 8899</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3467</t>
+          <t>0; 3845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>979; 9589</t>
+          <t>1073; 10077</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>4556</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>870; 8484</t>
+          <t>1139; 11029</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>973; 8829</t>
+          <t>1189; 10685</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>781</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3774</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 11425</t>
+          <t>971; 8309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3266</t>
+          <t>0; 4181</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 12017</t>
+          <t>1004; 8811</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>12391</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3938; 15834</t>
+          <t>3921; 16911</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>639; 6754</t>
+          <t>698; 7872</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5716; 19055</t>
+          <t>7257; 20649</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>11396</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2488; 13519</t>
+          <t>2393; 12915</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1848; 8572</t>
+          <t>2004; 9475</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5789; 17792</t>
+          <t>6394; 18793</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>926</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>677</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1603</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5181</t>
+          <t>0; 4185</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3568</t>
+          <t>0; 3660</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6211</t>
+          <t>0; 5590</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9082; 39461</t>
+          <t>18704; 41156</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5131; 14945</t>
+          <t>5196; 16190</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16077; 50284</t>
+          <t>27869; 51368</t>
         </is>
       </c>
     </row>
